--- a/backend/data/financials_by_company/0PL.F.xlsx
+++ b/backend/data/financials_by_company/0PL.F.xlsx
@@ -702,167 +702,175 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45504</v>
+        <v>44408</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>-40383.946105</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>0.010153</v>
       </c>
       <c r="D2" t="n">
-        <v>-8700486</v>
+        <v>-6989515</v>
       </c>
       <c r="E2" t="n">
-        <v>-270108</v>
+        <v>-3977450</v>
       </c>
       <c r="F2" t="n">
-        <v>-270108</v>
+        <v>-3977450</v>
       </c>
       <c r="G2" t="n">
-        <v>-11064855</v>
+        <v>-16562334</v>
       </c>
       <c r="H2" t="n">
-        <v>2109471</v>
+        <v>1812739</v>
       </c>
       <c r="I2" t="n">
-        <v>4602824</v>
+        <v>28054</v>
       </c>
       <c r="J2" t="n">
-        <v>-8970594</v>
+        <v>-10966965</v>
       </c>
       <c r="K2" t="n">
-        <v>-11080065</v>
+        <v>-12779704</v>
       </c>
       <c r="L2" t="n">
-        <v>285318</v>
+        <v>24934</v>
       </c>
       <c r="M2" t="n">
-        <v>285318</v>
+        <v>24934</v>
       </c>
       <c r="N2" t="n">
-        <v>-10794747</v>
+        <v>-12625267.946105</v>
       </c>
       <c r="O2" t="n">
-        <v>-11064855</v>
+        <v>-16562334</v>
       </c>
       <c r="P2" t="n">
-        <v>27438072</v>
+        <v>13861679</v>
       </c>
       <c r="Q2" t="n">
-        <v>-11350173</v>
+        <v>-12779704</v>
       </c>
       <c r="R2" t="n">
-        <v>203820258</v>
+        <v>150728622</v>
       </c>
       <c r="S2" t="n">
-        <v>203820258</v>
+        <v>150728622</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.05</v>
+        <v>-0.11</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.05</v>
+        <v>-0.11</v>
       </c>
       <c r="V2" t="n">
-        <v>-11064855</v>
+        <v>-16562334</v>
       </c>
       <c r="W2" t="n">
-        <v>-11064855</v>
+        <v>-16562334</v>
       </c>
       <c r="X2" t="n">
-        <v>-11064855</v>
+        <v>-16562334</v>
       </c>
       <c r="Y2" t="n">
-        <v>-11064855</v>
+        <v>-16562334</v>
       </c>
       <c r="Z2" t="n">
-        <v>-11064855</v>
-      </c>
-      <c r="AA2" t="inlineStr"/>
+        <v>-16562334</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>-169886</v>
+      </c>
       <c r="AB2" t="n">
-        <v>-11064855</v>
+        <v>-16732220</v>
       </c>
       <c r="AC2" t="n">
-        <v>-270108</v>
+        <v>-3977450</v>
       </c>
       <c r="AD2" t="n">
-        <v>-270108</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-95066</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>175042</v>
-      </c>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>-3977450</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>-3977450</v>
+      </c>
       <c r="AJ2" t="n">
-        <v>285318</v>
+        <v>24934</v>
       </c>
       <c r="AK2" t="n">
-        <v>285318</v>
+        <v>24934</v>
       </c>
       <c r="AL2" t="n">
-        <v>-11080065</v>
+        <v>-12779704</v>
       </c>
       <c r="AM2" t="n">
-        <v>21338084</v>
-      </c>
-      <c r="AN2" t="inlineStr"/>
+        <v>13861679</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>28054</v>
+      </c>
       <c r="AO2" t="n">
-        <v>612307</v>
+        <v>1812739</v>
       </c>
       <c r="AP2" t="n">
-        <v>612307</v>
+        <v>1812739</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>832817</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>832817</v>
       </c>
       <c r="AS2" t="n">
-        <v>612307</v>
+        <v>979922</v>
       </c>
       <c r="AT2" t="n">
-        <v>8265043</v>
+        <v>2757491</v>
       </c>
       <c r="AU2" t="n">
-        <v>12460734</v>
+        <v>9263395</v>
       </c>
       <c r="AV2" t="n">
-        <v>2009216</v>
+        <v>1472209</v>
       </c>
       <c r="AW2" t="n">
-        <v>10451518</v>
+        <v>7791186</v>
       </c>
       <c r="AX2" t="n">
-        <v>1857873</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>239869</v>
-      </c>
+        <v>2248484</v>
+      </c>
+      <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="n">
-        <v>8353776</v>
+        <v>5542702</v>
       </c>
       <c r="BA2" t="n">
-        <v>10258019</v>
+        <v>1053921</v>
       </c>
       <c r="BB2" t="n">
-        <v>6099988</v>
+        <v>28054</v>
       </c>
       <c r="BC2" t="n">
-        <v>16358007</v>
+        <v>1081975</v>
       </c>
       <c r="BD2" t="n">
-        <v>16358007</v>
+        <v>1081975</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45138</v>
+        <v>44773</v>
       </c>
       <c r="B3" t="n">
         <v>0</v>
@@ -871,164 +879,164 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-13719466</v>
+        <v>13704822</v>
       </c>
       <c r="E3" t="n">
-        <v>-524230</v>
+        <v>-25921985</v>
       </c>
       <c r="F3" t="n">
-        <v>-524230</v>
+        <v>-25921985</v>
       </c>
       <c r="G3" t="n">
-        <v>-16336473</v>
+        <v>-39716689</v>
       </c>
       <c r="H3" t="n">
-        <v>1729664</v>
+        <v>1608825</v>
       </c>
       <c r="I3" t="n">
-        <v>567274</v>
+        <v>239487</v>
       </c>
       <c r="J3" t="n">
-        <v>-14243696</v>
+        <v>-12217163</v>
       </c>
       <c r="K3" t="n">
-        <v>-15973360</v>
+        <v>-13825988</v>
       </c>
       <c r="L3" t="n">
-        <v>161117</v>
+        <v>31284</v>
       </c>
       <c r="M3" t="n">
-        <v>161117</v>
+        <v>31284</v>
       </c>
       <c r="N3" t="n">
-        <v>-15812243</v>
+        <v>-13794704</v>
       </c>
       <c r="O3" t="n">
-        <v>-16336473</v>
+        <v>-39716689</v>
       </c>
       <c r="P3" t="n">
-        <v>20084604</v>
+        <v>17445202</v>
       </c>
       <c r="Q3" t="n">
-        <v>-16500841</v>
+        <v>-39922973</v>
       </c>
       <c r="R3" t="n">
-        <v>176664492</v>
+        <v>155744354</v>
       </c>
       <c r="S3" t="n">
-        <v>176664492</v>
+        <v>155744354</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.09</v>
+        <v>-0.25</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.09</v>
+        <v>-0.25</v>
       </c>
       <c r="V3" t="n">
-        <v>-16336473</v>
+        <v>-39716689</v>
       </c>
       <c r="W3" t="n">
-        <v>-16336473</v>
+        <v>-39716689</v>
       </c>
       <c r="X3" t="n">
-        <v>-16336473</v>
+        <v>-39716689</v>
       </c>
       <c r="Y3" t="n">
-        <v>-16336473</v>
+        <v>-39716689</v>
       </c>
       <c r="Z3" t="n">
-        <v>-16336473</v>
-      </c>
-      <c r="AA3" t="inlineStr"/>
+        <v>-39716689</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
       <c r="AB3" t="n">
-        <v>-16336473</v>
+        <v>-39716689</v>
       </c>
       <c r="AC3" t="n">
-        <v>-524230</v>
+        <v>-25921985</v>
       </c>
       <c r="AD3" t="n">
-        <v>-527481</v>
+        <v>-26096985</v>
       </c>
       <c r="AE3" t="n">
-        <v>-181107</v>
+        <v>-12155</v>
       </c>
       <c r="AF3" t="n">
-        <v>346374</v>
+        <v>502397</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>25582433</v>
       </c>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="n">
-        <v>3251</v>
+        <v>175000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>161117</v>
+        <v>31284</v>
       </c>
       <c r="AK3" t="n">
-        <v>161117</v>
+        <v>31284</v>
       </c>
       <c r="AL3" t="n">
-        <v>-15973360</v>
+        <v>-13825988</v>
       </c>
       <c r="AM3" t="n">
-        <v>18458257</v>
+        <v>17445202</v>
       </c>
       <c r="AN3" t="n">
-        <v>926058</v>
+        <v>277286</v>
       </c>
       <c r="AO3" t="n">
-        <v>670591</v>
+        <v>1571026</v>
       </c>
       <c r="AP3" t="n">
-        <v>670591</v>
+        <v>1571026</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>805900</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>805900</v>
       </c>
       <c r="AS3" t="n">
-        <v>670591</v>
+        <v>765126</v>
       </c>
       <c r="AT3" t="n">
-        <v>7078280</v>
+        <v>4463527</v>
       </c>
       <c r="AU3" t="n">
-        <v>10709386</v>
+        <v>11133363</v>
       </c>
       <c r="AV3" t="n">
-        <v>1635280</v>
+        <v>1968641</v>
       </c>
       <c r="AW3" t="n">
-        <v>9074106</v>
+        <v>9164722</v>
       </c>
       <c r="AX3" t="n">
-        <v>1898015</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>221123</v>
-      </c>
+        <v>2816627</v>
+      </c>
+      <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="n">
-        <v>6954968</v>
+        <v>6348095</v>
       </c>
       <c r="BA3" t="n">
-        <v>2484897</v>
+        <v>3341928</v>
       </c>
       <c r="BB3" t="n">
-        <v>1626347</v>
+        <v>277286</v>
       </c>
       <c r="BC3" t="n">
-        <v>4111244</v>
+        <v>3619214</v>
       </c>
       <c r="BD3" t="n">
-        <v>4111244</v>
+        <v>3619214</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44773</v>
+        <v>45138</v>
       </c>
       <c r="B4" t="n">
         <v>0</v>
@@ -1037,327 +1045,319 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>13704822</v>
+        <v>-13719466</v>
       </c>
       <c r="E4" t="n">
-        <v>-25921985</v>
+        <v>-524230</v>
       </c>
       <c r="F4" t="n">
-        <v>-25921985</v>
+        <v>-524230</v>
       </c>
       <c r="G4" t="n">
-        <v>-39716689</v>
+        <v>-16336473</v>
       </c>
       <c r="H4" t="n">
-        <v>1608825</v>
+        <v>1729664</v>
       </c>
       <c r="I4" t="n">
-        <v>239487</v>
+        <v>567274</v>
       </c>
       <c r="J4" t="n">
-        <v>-12217163</v>
+        <v>-14243696</v>
       </c>
       <c r="K4" t="n">
-        <v>-13825988</v>
+        <v>-15973360</v>
       </c>
       <c r="L4" t="n">
-        <v>31284</v>
+        <v>161117</v>
       </c>
       <c r="M4" t="n">
-        <v>31284</v>
+        <v>161117</v>
       </c>
       <c r="N4" t="n">
-        <v>-13794704</v>
+        <v>-15812243</v>
       </c>
       <c r="O4" t="n">
-        <v>-39716689</v>
+        <v>-16336473</v>
       </c>
       <c r="P4" t="n">
-        <v>17445202</v>
+        <v>20084604</v>
       </c>
       <c r="Q4" t="n">
-        <v>-39922973</v>
+        <v>-16500841</v>
       </c>
       <c r="R4" t="n">
-        <v>155744354</v>
+        <v>176664492</v>
       </c>
       <c r="S4" t="n">
-        <v>155744354</v>
+        <v>176664492</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.25</v>
+        <v>-0.09</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.25</v>
+        <v>-0.09</v>
       </c>
       <c r="V4" t="n">
-        <v>-39716689</v>
+        <v>-16336473</v>
       </c>
       <c r="W4" t="n">
-        <v>-39716689</v>
+        <v>-16336473</v>
       </c>
       <c r="X4" t="n">
-        <v>-39716689</v>
+        <v>-16336473</v>
       </c>
       <c r="Y4" t="n">
-        <v>-39716689</v>
+        <v>-16336473</v>
       </c>
       <c r="Z4" t="n">
-        <v>-39716689</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
+        <v>-16336473</v>
+      </c>
+      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="n">
-        <v>-39716689</v>
+        <v>-16336473</v>
       </c>
       <c r="AC4" t="n">
-        <v>-25921985</v>
+        <v>-524230</v>
       </c>
       <c r="AD4" t="n">
-        <v>-26096985</v>
+        <v>-527481</v>
       </c>
       <c r="AE4" t="n">
-        <v>-12155</v>
+        <v>-181107</v>
       </c>
       <c r="AF4" t="n">
-        <v>502397</v>
+        <v>346374</v>
       </c>
       <c r="AG4" t="n">
-        <v>25582433</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="n">
-        <v>175000</v>
+        <v>3251</v>
       </c>
       <c r="AJ4" t="n">
-        <v>31284</v>
+        <v>161117</v>
       </c>
       <c r="AK4" t="n">
-        <v>31284</v>
+        <v>161117</v>
       </c>
       <c r="AL4" t="n">
-        <v>-13825988</v>
+        <v>-15973360</v>
       </c>
       <c r="AM4" t="n">
-        <v>17445202</v>
+        <v>18458257</v>
       </c>
       <c r="AN4" t="n">
-        <v>277286</v>
+        <v>926058</v>
       </c>
       <c r="AO4" t="n">
-        <v>1571026</v>
+        <v>670591</v>
       </c>
       <c r="AP4" t="n">
-        <v>1571026</v>
+        <v>670591</v>
       </c>
       <c r="AQ4" t="n">
-        <v>805900</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>805900</v>
+        <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>765126</v>
+        <v>670591</v>
       </c>
       <c r="AT4" t="n">
-        <v>4463527</v>
+        <v>7078280</v>
       </c>
       <c r="AU4" t="n">
-        <v>11133363</v>
+        <v>10709386</v>
       </c>
       <c r="AV4" t="n">
-        <v>1968641</v>
+        <v>1635280</v>
       </c>
       <c r="AW4" t="n">
-        <v>9164722</v>
+        <v>9074106</v>
       </c>
       <c r="AX4" t="n">
-        <v>2816627</v>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+        <v>1898015</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>221123</v>
+      </c>
       <c r="AZ4" t="n">
-        <v>6348095</v>
+        <v>6954968</v>
       </c>
       <c r="BA4" t="n">
-        <v>3341928</v>
+        <v>2484897</v>
       </c>
       <c r="BB4" t="n">
-        <v>277286</v>
+        <v>1626347</v>
       </c>
       <c r="BC4" t="n">
-        <v>3619214</v>
+        <v>4111244</v>
       </c>
       <c r="BD4" t="n">
-        <v>3619214</v>
+        <v>4111244</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44408</v>
+        <v>45504</v>
       </c>
       <c r="B5" t="n">
-        <v>-40383.946105</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0.010153</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-6989515</v>
+        <v>-8700486</v>
       </c>
       <c r="E5" t="n">
-        <v>-3977450</v>
+        <v>-270108</v>
       </c>
       <c r="F5" t="n">
-        <v>-3977450</v>
+        <v>-270108</v>
       </c>
       <c r="G5" t="n">
-        <v>-16562334</v>
+        <v>-11064855</v>
       </c>
       <c r="H5" t="n">
-        <v>1812739</v>
+        <v>2109471</v>
       </c>
       <c r="I5" t="n">
-        <v>28054</v>
+        <v>4602824</v>
       </c>
       <c r="J5" t="n">
-        <v>-10966965</v>
+        <v>-8970594</v>
       </c>
       <c r="K5" t="n">
-        <v>-12779704</v>
+        <v>-11080065</v>
       </c>
       <c r="L5" t="n">
-        <v>24934</v>
+        <v>285318</v>
       </c>
       <c r="M5" t="n">
-        <v>24934</v>
+        <v>285318</v>
       </c>
       <c r="N5" t="n">
-        <v>-12625267.946105</v>
+        <v>-10794747</v>
       </c>
       <c r="O5" t="n">
-        <v>-16562334</v>
+        <v>-11064855</v>
       </c>
       <c r="P5" t="n">
-        <v>13861679</v>
+        <v>27438072</v>
       </c>
       <c r="Q5" t="n">
-        <v>-12779704</v>
+        <v>-11350173</v>
       </c>
       <c r="R5" t="n">
-        <v>150728622</v>
+        <v>203820258</v>
       </c>
       <c r="S5" t="n">
-        <v>150728622</v>
+        <v>203820258</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.11</v>
+        <v>-0.05</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.11</v>
+        <v>-0.05</v>
       </c>
       <c r="V5" t="n">
-        <v>-16562334</v>
+        <v>-11064855</v>
       </c>
       <c r="W5" t="n">
-        <v>-16562334</v>
+        <v>-11064855</v>
       </c>
       <c r="X5" t="n">
-        <v>-16562334</v>
+        <v>-11064855</v>
       </c>
       <c r="Y5" t="n">
-        <v>-16562334</v>
+        <v>-11064855</v>
       </c>
       <c r="Z5" t="n">
-        <v>-16562334</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>-169886</v>
-      </c>
+        <v>-11064855</v>
+      </c>
+      <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="n">
-        <v>-16732220</v>
+        <v>-11064855</v>
       </c>
       <c r="AC5" t="n">
-        <v>-3977450</v>
+        <v>-270108</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>-270108</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>-95066</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>-3977450</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>-3977450</v>
-      </c>
+        <v>175042</v>
+      </c>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="n">
-        <v>24934</v>
+        <v>285318</v>
       </c>
       <c r="AK5" t="n">
-        <v>24934</v>
+        <v>285318</v>
       </c>
       <c r="AL5" t="n">
-        <v>-12779704</v>
+        <v>-11080065</v>
       </c>
       <c r="AM5" t="n">
-        <v>13861679</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>28054</v>
-      </c>
+        <v>21338084</v>
+      </c>
+      <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="n">
-        <v>1812739</v>
+        <v>612307</v>
       </c>
       <c r="AP5" t="n">
-        <v>1812739</v>
+        <v>612307</v>
       </c>
       <c r="AQ5" t="n">
-        <v>832817</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>832817</v>
+        <v>0</v>
       </c>
       <c r="AS5" t="n">
-        <v>979922</v>
+        <v>612307</v>
       </c>
       <c r="AT5" t="n">
-        <v>2757491</v>
+        <v>8265043</v>
       </c>
       <c r="AU5" t="n">
-        <v>9263395</v>
+        <v>12460734</v>
       </c>
       <c r="AV5" t="n">
-        <v>1472209</v>
+        <v>2009216</v>
       </c>
       <c r="AW5" t="n">
-        <v>7791186</v>
+        <v>10451518</v>
       </c>
       <c r="AX5" t="n">
-        <v>2248484</v>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+        <v>1857873</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>239869</v>
+      </c>
       <c r="AZ5" t="n">
-        <v>5542702</v>
+        <v>8353776</v>
       </c>
       <c r="BA5" t="n">
-        <v>1053921</v>
+        <v>10258019</v>
       </c>
       <c r="BB5" t="n">
-        <v>28054</v>
+        <v>6099988</v>
       </c>
       <c r="BC5" t="n">
-        <v>1081975</v>
+        <v>16358007</v>
       </c>
       <c r="BD5" t="n">
-        <v>1081975</v>
+        <v>16358007</v>
       </c>
     </row>
   </sheetData>
@@ -1688,713 +1688,713 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45504</v>
+        <v>44408</v>
       </c>
       <c r="B2" t="n">
-        <v>218388237</v>
+        <v>150728622</v>
       </c>
       <c r="C2" t="n">
-        <v>218388237</v>
+        <v>150728622</v>
       </c>
       <c r="D2" t="n">
-        <v>380926</v>
+        <v>985920</v>
       </c>
       <c r="E2" t="n">
-        <v>9505094</v>
+        <v>14800413</v>
       </c>
       <c r="F2" t="n">
-        <v>13970849</v>
+        <v>46838346</v>
       </c>
       <c r="G2" t="n">
-        <v>9874071</v>
+        <v>12840798</v>
       </c>
       <c r="H2" t="n">
-        <v>9505094</v>
+        <v>14800413</v>
       </c>
       <c r="I2" t="n">
-        <v>380926</v>
+        <v>985920</v>
       </c>
       <c r="J2" t="n">
-        <v>13970849</v>
+        <v>46838346</v>
       </c>
       <c r="K2" t="n">
-        <v>13970849</v>
+        <v>46838346</v>
       </c>
       <c r="L2" t="n">
-        <v>13970849</v>
+        <v>46838346</v>
       </c>
       <c r="M2" t="n">
-        <v>13970849</v>
+        <v>46838346</v>
       </c>
       <c r="N2" t="n">
-        <v>-146565553</v>
+        <v>-79447536</v>
       </c>
       <c r="O2" t="n">
-        <v>16163950</v>
+        <v>11688151</v>
       </c>
       <c r="P2" t="n">
-        <v>144372452</v>
+        <v>114597731</v>
       </c>
       <c r="Q2" t="n">
-        <v>144372452</v>
+        <v>114597731</v>
       </c>
       <c r="R2" t="n">
-        <v>10971321</v>
+        <v>2560078</v>
       </c>
       <c r="S2" t="n">
-        <v>3346105</v>
-      </c>
-      <c r="T2" t="n">
-        <v>3155579</v>
-      </c>
-      <c r="U2" t="n">
-        <v>3155579</v>
-      </c>
+        <v>677275</v>
+      </c>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>190526</v>
+        <v>677275</v>
       </c>
       <c r="W2" t="n">
-        <v>190526</v>
+        <v>677275</v>
       </c>
       <c r="X2" t="n">
-        <v>7625216</v>
+        <v>1882803</v>
       </c>
       <c r="Y2" t="n">
-        <v>3443524</v>
+        <v>308547</v>
       </c>
       <c r="Z2" t="n">
-        <v>3443524</v>
+        <v>308547</v>
       </c>
       <c r="AA2" t="n">
-        <v>190400</v>
+        <v>308645</v>
       </c>
       <c r="AB2" t="n">
-        <v>190400</v>
+        <v>308645</v>
       </c>
       <c r="AC2" t="n">
-        <v>3991292</v>
-      </c>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
+        <v>1265611</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1265611</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1265611</v>
+      </c>
       <c r="AF2" t="n">
-        <v>24942170</v>
+        <v>49398424</v>
       </c>
       <c r="AG2" t="n">
-        <v>7442883</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>496868</v>
-      </c>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
+        <v>34674823</v>
+      </c>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="n">
+        <v>218750</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>218750</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>218750</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>218750</v>
+      </c>
       <c r="AM2" t="n">
-        <v>4465755</v>
+        <v>32037933</v>
       </c>
       <c r="AN2" t="n">
-        <v>4465755</v>
-      </c>
-      <c r="AO2" t="inlineStr"/>
+        <v>6455500</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>25582433</v>
+      </c>
       <c r="AP2" t="n">
-        <v>2480260</v>
+        <v>2418140</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-2186149</v>
+        <v>-1325152</v>
       </c>
       <c r="AR2" t="n">
-        <v>4666409</v>
+        <v>3743292</v>
       </c>
       <c r="AS2" t="n">
-        <v>158268</v>
+        <v>229427</v>
       </c>
       <c r="AT2" t="n">
-        <v>2242316</v>
+        <v>23800</v>
       </c>
       <c r="AU2" t="n">
-        <v>1921521</v>
+        <v>2576796</v>
       </c>
       <c r="AV2" t="n">
-        <v>344304</v>
+        <v>913269</v>
       </c>
       <c r="AW2" t="n">
-        <v>17499287</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>371309</v>
-      </c>
+        <v>14723601</v>
+      </c>
+      <c r="AX2" t="inlineStr"/>
       <c r="AY2" t="n">
-        <v>949012</v>
+        <v>355575</v>
       </c>
       <c r="AZ2" t="n">
-        <v>3688246</v>
-      </c>
-      <c r="BA2" t="inlineStr"/>
+        <v>1458122</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>142499</v>
+      </c>
       <c r="BB2" t="n">
-        <v>3312593</v>
+        <v>1315623</v>
       </c>
       <c r="BC2" t="n">
-        <v>375653</v>
+        <v>142499</v>
       </c>
       <c r="BD2" t="n">
-        <v>3862199</v>
-      </c>
-      <c r="BE2" t="inlineStr"/>
+        <v>3257411</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>2703419</v>
+      </c>
       <c r="BF2" t="n">
-        <v>593209</v>
+        <v>317272</v>
       </c>
       <c r="BG2" t="n">
-        <v>3268990</v>
+        <v>236720</v>
       </c>
       <c r="BH2" t="n">
-        <v>8628521</v>
-      </c>
-      <c r="BI2" t="inlineStr"/>
+        <v>9652493</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>0</v>
+      </c>
       <c r="BJ2" t="n">
-        <v>8628521</v>
-      </c>
-      <c r="BK2" t="inlineStr"/>
+        <v>9652493</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>9652493</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45138</v>
+        <v>44773</v>
       </c>
       <c r="B3" t="n">
-        <v>197779517</v>
+        <v>163179222</v>
       </c>
       <c r="C3" t="n">
-        <v>197779517</v>
+        <v>163179222</v>
       </c>
       <c r="D3" t="n">
+        <v>677276</v>
+      </c>
+      <c r="E3" t="n">
+        <v>8895575</v>
+      </c>
+      <c r="F3" t="n">
+        <v>14545175</v>
+      </c>
+      <c r="G3" t="n">
+        <v>6790993</v>
+      </c>
+      <c r="H3" t="n">
+        <v>8895575</v>
+      </c>
+      <c r="I3" t="n">
+        <v>677276</v>
+      </c>
+      <c r="J3" t="n">
+        <v>14545175</v>
+      </c>
+      <c r="K3" t="n">
+        <v>14545175</v>
+      </c>
+      <c r="L3" t="n">
+        <v>14545175</v>
+      </c>
+      <c r="M3" t="n">
+        <v>14545175</v>
+      </c>
+      <c r="N3" t="n">
+        <v>-119164225</v>
+      </c>
+      <c r="O3" t="n">
+        <v>13912816</v>
+      </c>
+      <c r="P3" t="n">
+        <v>119796584</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>119796584</v>
+      </c>
+      <c r="R3" t="n">
+        <v>3513009</v>
+      </c>
+      <c r="S3" t="n">
         <v>356841</v>
       </c>
-      <c r="E3" t="n">
-        <v>9899198</v>
-      </c>
-      <c r="F3" t="n">
-        <v>14742898</v>
-      </c>
-      <c r="G3" t="n">
-        <v>8084175</v>
-      </c>
-      <c r="H3" t="n">
-        <v>9899198</v>
-      </c>
-      <c r="I3" t="n">
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="n">
         <v>356841</v>
       </c>
-      <c r="J3" t="n">
-        <v>14742898</v>
-      </c>
-      <c r="K3" t="n">
-        <v>14742898</v>
-      </c>
-      <c r="L3" t="n">
-        <v>14742898</v>
-      </c>
-      <c r="M3" t="n">
-        <v>14742898</v>
-      </c>
-      <c r="N3" t="n">
-        <v>-135500698</v>
-      </c>
-      <c r="O3" t="n">
-        <v>14420259</v>
-      </c>
-      <c r="P3" t="n">
-        <v>135823337</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>135823337</v>
-      </c>
-      <c r="R3" t="n">
-        <v>4255932</v>
-      </c>
-      <c r="S3" t="n">
-        <v>535590</v>
-      </c>
-      <c r="T3" t="n">
-        <v>411232</v>
-      </c>
-      <c r="U3" t="n">
-        <v>411232</v>
-      </c>
-      <c r="V3" t="n">
-        <v>124358</v>
-      </c>
       <c r="W3" t="n">
-        <v>124358</v>
+        <v>356841</v>
       </c>
       <c r="X3" t="n">
-        <v>3720342</v>
+        <v>3156168</v>
       </c>
       <c r="Y3" t="n">
-        <v>968509</v>
+        <v>196651</v>
       </c>
       <c r="Z3" t="n">
-        <v>968509</v>
+        <v>196651</v>
       </c>
       <c r="AA3" t="n">
-        <v>232483</v>
+        <v>320435</v>
       </c>
       <c r="AB3" t="n">
-        <v>232483</v>
+        <v>320435</v>
       </c>
       <c r="AC3" t="n">
-        <v>2519350</v>
+        <v>2639082</v>
       </c>
       <c r="AD3" t="n">
-        <v>2519350</v>
+        <v>2639082</v>
       </c>
       <c r="AE3" t="n">
-        <v>2519350</v>
+        <v>2639082</v>
       </c>
       <c r="AF3" t="n">
-        <v>18998830</v>
+        <v>18058184</v>
       </c>
       <c r="AG3" t="n">
-        <v>7194313</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
+        <v>8111023</v>
+      </c>
+      <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>393750</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="inlineStr"/>
+        <v>393750</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>393750</v>
+      </c>
       <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="n">
-        <v>4843700</v>
+        <v>5649600</v>
       </c>
       <c r="AN3" t="n">
-        <v>4843700</v>
-      </c>
-      <c r="AO3" t="inlineStr"/>
+        <v>5649600</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
       <c r="AP3" t="n">
-        <v>2350613</v>
+        <v>2067673</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-2002723</v>
+        <v>-1805924</v>
       </c>
       <c r="AR3" t="n">
-        <v>4353336</v>
+        <v>3873597</v>
       </c>
       <c r="AS3" t="n">
-        <v>244178</v>
+        <v>211639</v>
       </c>
       <c r="AT3" t="n">
-        <v>1564316</v>
+        <v>351145</v>
       </c>
       <c r="AU3" t="n">
-        <v>2258046</v>
+        <v>2720981</v>
       </c>
       <c r="AV3" t="n">
-        <v>286796</v>
+        <v>589832</v>
       </c>
       <c r="AW3" t="n">
-        <v>11804517</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
+        <v>9947161</v>
+      </c>
+      <c r="AX3" t="inlineStr"/>
       <c r="AY3" t="n">
-        <v>1026668</v>
+        <v>668650</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1602971</v>
-      </c>
-      <c r="BA3" t="inlineStr"/>
+        <v>1106034</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>379244</v>
+      </c>
       <c r="BB3" t="n">
-        <v>882541</v>
+        <v>726790</v>
       </c>
       <c r="BC3" t="n">
-        <v>720430</v>
+        <v>379244</v>
       </c>
       <c r="BD3" t="n">
-        <v>847429</v>
-      </c>
-      <c r="BE3" t="inlineStr"/>
+        <v>1895156</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>1000000</v>
+      </c>
       <c r="BF3" t="n">
-        <v>334503</v>
+        <v>170551</v>
       </c>
       <c r="BG3" t="n">
-        <v>512926</v>
+        <v>724605</v>
       </c>
       <c r="BH3" t="n">
-        <v>8327449</v>
+        <v>6277321</v>
       </c>
       <c r="BI3" t="inlineStr"/>
       <c r="BJ3" t="n">
-        <v>8327449</v>
+        <v>6277321</v>
       </c>
       <c r="BK3" t="n">
-        <v>8327449</v>
+        <v>6277321</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44773</v>
+        <v>45138</v>
       </c>
       <c r="B4" t="n">
-        <v>163179222</v>
+        <v>197779517</v>
       </c>
       <c r="C4" t="n">
-        <v>163179222</v>
+        <v>197779517</v>
       </c>
       <c r="D4" t="n">
-        <v>677276</v>
+        <v>356841</v>
       </c>
       <c r="E4" t="n">
-        <v>8895575</v>
+        <v>9899198</v>
       </c>
       <c r="F4" t="n">
-        <v>14545175</v>
+        <v>14742898</v>
       </c>
       <c r="G4" t="n">
-        <v>6790993</v>
+        <v>8084175</v>
       </c>
       <c r="H4" t="n">
-        <v>8895575</v>
+        <v>9899198</v>
       </c>
       <c r="I4" t="n">
-        <v>677276</v>
+        <v>356841</v>
       </c>
       <c r="J4" t="n">
-        <v>14545175</v>
+        <v>14742898</v>
       </c>
       <c r="K4" t="n">
-        <v>14545175</v>
+        <v>14742898</v>
       </c>
       <c r="L4" t="n">
-        <v>14545175</v>
+        <v>14742898</v>
       </c>
       <c r="M4" t="n">
-        <v>14545175</v>
+        <v>14742898</v>
       </c>
       <c r="N4" t="n">
-        <v>-119164225</v>
+        <v>-135500698</v>
       </c>
       <c r="O4" t="n">
-        <v>13912816</v>
+        <v>14420259</v>
       </c>
       <c r="P4" t="n">
-        <v>119796584</v>
+        <v>135823337</v>
       </c>
       <c r="Q4" t="n">
-        <v>119796584</v>
+        <v>135823337</v>
       </c>
       <c r="R4" t="n">
-        <v>3513009</v>
+        <v>4255932</v>
       </c>
       <c r="S4" t="n">
-        <v>356841</v>
-      </c>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
+        <v>535590</v>
+      </c>
+      <c r="T4" t="n">
+        <v>411232</v>
+      </c>
+      <c r="U4" t="n">
+        <v>411232</v>
+      </c>
       <c r="V4" t="n">
-        <v>356841</v>
+        <v>124358</v>
       </c>
       <c r="W4" t="n">
-        <v>356841</v>
+        <v>124358</v>
       </c>
       <c r="X4" t="n">
-        <v>3156168</v>
+        <v>3720342</v>
       </c>
       <c r="Y4" t="n">
-        <v>196651</v>
+        <v>968509</v>
       </c>
       <c r="Z4" t="n">
-        <v>196651</v>
+        <v>968509</v>
       </c>
       <c r="AA4" t="n">
-        <v>320435</v>
+        <v>232483</v>
       </c>
       <c r="AB4" t="n">
-        <v>320435</v>
+        <v>232483</v>
       </c>
       <c r="AC4" t="n">
-        <v>2639082</v>
+        <v>2519350</v>
       </c>
       <c r="AD4" t="n">
-        <v>2639082</v>
+        <v>2519350</v>
       </c>
       <c r="AE4" t="n">
-        <v>2639082</v>
+        <v>2519350</v>
       </c>
       <c r="AF4" t="n">
-        <v>18058184</v>
+        <v>18998830</v>
       </c>
       <c r="AG4" t="n">
-        <v>8111023</v>
-      </c>
-      <c r="AH4" t="inlineStr"/>
+        <v>7194313</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
       <c r="AI4" t="n">
-        <v>393750</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>393750</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>393750</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="n">
-        <v>5649600</v>
+        <v>4843700</v>
       </c>
       <c r="AN4" t="n">
-        <v>5649600</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
+        <v>4843700</v>
+      </c>
+      <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="n">
-        <v>2067673</v>
+        <v>2350613</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-1805924</v>
+        <v>-2002723</v>
       </c>
       <c r="AR4" t="n">
-        <v>3873597</v>
+        <v>4353336</v>
       </c>
       <c r="AS4" t="n">
-        <v>211639</v>
+        <v>244178</v>
       </c>
       <c r="AT4" t="n">
-        <v>351145</v>
+        <v>1564316</v>
       </c>
       <c r="AU4" t="n">
-        <v>2720981</v>
+        <v>2258046</v>
       </c>
       <c r="AV4" t="n">
-        <v>589832</v>
+        <v>286796</v>
       </c>
       <c r="AW4" t="n">
-        <v>9947161</v>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+        <v>11804517</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
       <c r="AY4" t="n">
-        <v>668650</v>
+        <v>1026668</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1106034</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>379244</v>
-      </c>
+        <v>1602971</v>
+      </c>
+      <c r="BA4" t="inlineStr"/>
       <c r="BB4" t="n">
-        <v>726790</v>
+        <v>882541</v>
       </c>
       <c r="BC4" t="n">
-        <v>379244</v>
+        <v>720430</v>
       </c>
       <c r="BD4" t="n">
-        <v>1895156</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1000000</v>
-      </c>
+        <v>847429</v>
+      </c>
+      <c r="BE4" t="inlineStr"/>
       <c r="BF4" t="n">
-        <v>170551</v>
+        <v>334503</v>
       </c>
       <c r="BG4" t="n">
-        <v>724605</v>
+        <v>512926</v>
       </c>
       <c r="BH4" t="n">
-        <v>6277321</v>
+        <v>8327449</v>
       </c>
       <c r="BI4" t="inlineStr"/>
       <c r="BJ4" t="n">
-        <v>6277321</v>
+        <v>8327449</v>
       </c>
       <c r="BK4" t="n">
-        <v>6277321</v>
+        <v>8327449</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44408</v>
+        <v>45504</v>
       </c>
       <c r="B5" t="n">
-        <v>150728622</v>
+        <v>218388237</v>
       </c>
       <c r="C5" t="n">
-        <v>150728622</v>
+        <v>218388237</v>
       </c>
       <c r="D5" t="n">
-        <v>985920</v>
+        <v>380926</v>
       </c>
       <c r="E5" t="n">
-        <v>14800413</v>
+        <v>9505094</v>
       </c>
       <c r="F5" t="n">
-        <v>46838346</v>
+        <v>13970849</v>
       </c>
       <c r="G5" t="n">
-        <v>12840798</v>
+        <v>9874071</v>
       </c>
       <c r="H5" t="n">
-        <v>14800413</v>
+        <v>9505094</v>
       </c>
       <c r="I5" t="n">
-        <v>985920</v>
+        <v>380926</v>
       </c>
       <c r="J5" t="n">
-        <v>46838346</v>
+        <v>13970849</v>
       </c>
       <c r="K5" t="n">
-        <v>46838346</v>
+        <v>13970849</v>
       </c>
       <c r="L5" t="n">
-        <v>46838346</v>
+        <v>13970849</v>
       </c>
       <c r="M5" t="n">
-        <v>46838346</v>
+        <v>13970849</v>
       </c>
       <c r="N5" t="n">
-        <v>-79447536</v>
+        <v>-146565553</v>
       </c>
       <c r="O5" t="n">
-        <v>11688151</v>
+        <v>16163950</v>
       </c>
       <c r="P5" t="n">
-        <v>114597731</v>
+        <v>144372452</v>
       </c>
       <c r="Q5" t="n">
-        <v>114597731</v>
+        <v>144372452</v>
       </c>
       <c r="R5" t="n">
-        <v>2560078</v>
+        <v>10971321</v>
       </c>
       <c r="S5" t="n">
-        <v>677275</v>
-      </c>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
+        <v>3346105</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3155579</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3155579</v>
+      </c>
       <c r="V5" t="n">
-        <v>677275</v>
+        <v>190526</v>
       </c>
       <c r="W5" t="n">
-        <v>677275</v>
+        <v>190526</v>
       </c>
       <c r="X5" t="n">
-        <v>1882803</v>
+        <v>7625216</v>
       </c>
       <c r="Y5" t="n">
-        <v>308547</v>
+        <v>3443524</v>
       </c>
       <c r="Z5" t="n">
-        <v>308547</v>
+        <v>3443524</v>
       </c>
       <c r="AA5" t="n">
-        <v>308645</v>
+        <v>190400</v>
       </c>
       <c r="AB5" t="n">
-        <v>308645</v>
+        <v>190400</v>
       </c>
       <c r="AC5" t="n">
-        <v>1265611</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1265611</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1265611</v>
-      </c>
+        <v>3991292</v>
+      </c>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="n">
-        <v>49398424</v>
+        <v>24942170</v>
       </c>
       <c r="AG5" t="n">
-        <v>34674823</v>
-      </c>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="n">
-        <v>218750</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>218750</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>218750</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>218750</v>
-      </c>
+        <v>7442883</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>496868</v>
+      </c>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="n">
-        <v>32037933</v>
+        <v>4465755</v>
       </c>
       <c r="AN5" t="n">
-        <v>6455500</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>25582433</v>
-      </c>
+        <v>4465755</v>
+      </c>
+      <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="n">
-        <v>2418140</v>
+        <v>2480260</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-1325152</v>
+        <v>-2186149</v>
       </c>
       <c r="AR5" t="n">
-        <v>3743292</v>
+        <v>4666409</v>
       </c>
       <c r="AS5" t="n">
-        <v>229427</v>
+        <v>158268</v>
       </c>
       <c r="AT5" t="n">
-        <v>23800</v>
+        <v>2242316</v>
       </c>
       <c r="AU5" t="n">
-        <v>2576796</v>
+        <v>1921521</v>
       </c>
       <c r="AV5" t="n">
-        <v>913269</v>
+        <v>344304</v>
       </c>
       <c r="AW5" t="n">
-        <v>14723601</v>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+        <v>17499287</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>371309</v>
+      </c>
       <c r="AY5" t="n">
-        <v>355575</v>
+        <v>949012</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1458122</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>142499</v>
-      </c>
+        <v>3688246</v>
+      </c>
+      <c r="BA5" t="inlineStr"/>
       <c r="BB5" t="n">
-        <v>1315623</v>
+        <v>3312593</v>
       </c>
       <c r="BC5" t="n">
-        <v>142499</v>
+        <v>375653</v>
       </c>
       <c r="BD5" t="n">
-        <v>3257411</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>2703419</v>
-      </c>
+        <v>3862199</v>
+      </c>
+      <c r="BE5" t="inlineStr"/>
       <c r="BF5" t="n">
-        <v>317272</v>
+        <v>593209</v>
       </c>
       <c r="BG5" t="n">
-        <v>236720</v>
+        <v>3268990</v>
       </c>
       <c r="BH5" t="n">
-        <v>9652493</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>0</v>
-      </c>
+        <v>8628521</v>
+      </c>
+      <c r="BI5" t="inlineStr"/>
       <c r="BJ5" t="n">
-        <v>9652493</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>9652493</v>
-      </c>
+        <v>8628521</v>
+      </c>
+      <c r="BK5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2634,195 +2634,193 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45504</v>
+        <v>44408</v>
       </c>
       <c r="B2" t="n">
-        <v>-8573563</v>
+        <v>-12261429</v>
       </c>
       <c r="C2" t="n">
-        <v>-381427</v>
+        <v>-514964</v>
       </c>
       <c r="D2" t="n">
-        <v>9256062</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-429755</v>
+        <v>-566592</v>
       </c>
       <c r="F2" t="n">
-        <v>8628521</v>
+        <v>9652493</v>
       </c>
       <c r="G2" t="n">
-        <v>8327449</v>
+        <v>22407251</v>
       </c>
       <c r="H2" t="n">
-        <v>301072</v>
+        <v>-12754758</v>
       </c>
       <c r="I2" t="n">
-        <v>8874635</v>
+        <v>-514964</v>
       </c>
       <c r="J2" t="n">
-        <v>8874635</v>
+        <v>-514964</v>
       </c>
       <c r="K2" t="n">
-        <v>9256062</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>9256062</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-381427</v>
+        <v>-514964</v>
       </c>
       <c r="N2" t="n">
-        <v>-381427</v>
+        <v>-514964</v>
       </c>
       <c r="O2" t="n">
-        <v>-381427</v>
+        <v>-514964</v>
       </c>
       <c r="P2" t="n">
-        <v>-429755</v>
+        <v>-544957</v>
       </c>
       <c r="Q2" t="n">
-        <v>-429755</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
+        <v>-544957</v>
+      </c>
+      <c r="R2" t="n">
+        <v>21635</v>
+      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
       <c r="U2" t="n">
-        <v>-427955</v>
+        <v>-75000</v>
       </c>
       <c r="V2" t="n">
-        <v>-427955</v>
+        <v>-75000</v>
       </c>
       <c r="W2" t="n">
-        <v>-1800</v>
+        <v>-491592</v>
       </c>
       <c r="X2" t="n">
-        <v>-1800</v>
+        <v>-491592</v>
       </c>
       <c r="Y2" t="n">
-        <v>-8143808</v>
+        <v>-11694837</v>
       </c>
       <c r="Z2" t="n">
-        <v>-8143808</v>
+        <v>-11694837</v>
       </c>
       <c r="AA2" t="n">
-        <v>-517696</v>
+        <v>-2196307</v>
       </c>
       <c r="AB2" t="n">
-        <v>5470215</v>
+        <v>-119742</v>
       </c>
       <c r="AC2" t="n">
-        <v>1471942</v>
+        <v>-1083086</v>
       </c>
       <c r="AD2" t="n">
-        <v>77656</v>
+        <v>601040</v>
       </c>
       <c r="AE2" t="n">
-        <v>-4522739</v>
+        <v>39744</v>
       </c>
       <c r="AF2" t="n">
-        <v>-3014770</v>
+        <v>-1634263</v>
       </c>
       <c r="AG2" t="n">
-        <v>22420</v>
+        <v>99065</v>
       </c>
       <c r="AH2" t="n">
-        <v>1036744</v>
+        <v>1180231</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>3977450</v>
       </c>
       <c r="AJ2" t="n">
-        <v>175042</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>2109471</v>
+        <v>1812739</v>
       </c>
       <c r="AL2" t="n">
-        <v>2109471</v>
+        <v>1812739</v>
       </c>
       <c r="AM2" t="n">
-        <v>805900</v>
+        <v>832817</v>
       </c>
       <c r="AN2" t="n">
-        <v>805900</v>
+        <v>832817</v>
       </c>
       <c r="AO2" t="n">
-        <v>1303571</v>
+        <v>979922</v>
       </c>
       <c r="AP2" t="n">
-        <v>95066</v>
+        <v>-5681</v>
       </c>
       <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="n">
-        <v>95066</v>
+        <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>-11064855</v>
+        <v>-16562334</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45138</v>
+        <v>44773</v>
       </c>
       <c r="B3" t="n">
-        <v>-13567861</v>
+        <v>-9367198</v>
       </c>
       <c r="C3" t="n">
-        <v>-362672</v>
+        <v>-367652</v>
       </c>
       <c r="D3" t="n">
-        <v>15583660</v>
+        <v>6359678</v>
       </c>
       <c r="E3" t="n">
-        <v>-32539</v>
+        <v>-95757</v>
       </c>
       <c r="F3" t="n">
-        <v>8327449</v>
+        <v>6277321</v>
       </c>
       <c r="G3" t="n">
-        <v>6277321</v>
+        <v>9652493</v>
       </c>
       <c r="H3" t="n">
-        <v>2050128</v>
+        <v>-3375172</v>
       </c>
       <c r="I3" t="n">
-        <v>15220988</v>
+        <v>5992026</v>
       </c>
       <c r="J3" t="n">
-        <v>15220988</v>
+        <v>5992026</v>
       </c>
       <c r="K3" t="n">
-        <v>15583660</v>
+        <v>6359678</v>
       </c>
       <c r="L3" t="n">
-        <v>15583660</v>
+        <v>6359678</v>
       </c>
       <c r="M3" t="n">
-        <v>-362672</v>
+        <v>-367652</v>
       </c>
       <c r="N3" t="n">
-        <v>-362672</v>
+        <v>-367652</v>
       </c>
       <c r="O3" t="n">
-        <v>-362672</v>
+        <v>-367652</v>
       </c>
       <c r="P3" t="n">
-        <v>364462</v>
+        <v>-95757</v>
       </c>
       <c r="Q3" t="n">
-        <v>364462</v>
+        <v>-95757</v>
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>397001</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>397001</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -2831,52 +2829,52 @@
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-32539</v>
+        <v>-95757</v>
       </c>
       <c r="X3" t="n">
-        <v>-32539</v>
+        <v>-95757</v>
       </c>
       <c r="Y3" t="n">
-        <v>-13535322</v>
+        <v>-9271441</v>
       </c>
       <c r="Z3" t="n">
-        <v>-13535322</v>
+        <v>-9271441</v>
       </c>
       <c r="AA3" t="n">
-        <v>-425516</v>
+        <v>1784673</v>
       </c>
       <c r="AB3" t="n">
-        <v>1183090</v>
+        <v>-111896</v>
       </c>
       <c r="AC3" t="n">
-        <v>-99732</v>
+        <v>1373471</v>
       </c>
       <c r="AD3" t="n">
-        <v>-358018</v>
+        <v>-313075</v>
       </c>
       <c r="AE3" t="n">
-        <v>-2198583</v>
+        <v>-526082</v>
       </c>
       <c r="AF3" t="n">
-        <v>1047727</v>
+        <v>1362255</v>
       </c>
       <c r="AG3" t="n">
-        <v>22237</v>
+        <v>66632</v>
       </c>
       <c r="AH3" t="n">
-        <v>950536</v>
+        <v>1063840</v>
       </c>
       <c r="AI3" t="n">
-        <v>-58333</v>
+        <v>-175000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>346374</v>
+        <v>26084830</v>
       </c>
       <c r="AK3" t="n">
-        <v>1729664</v>
+        <v>1608825</v>
       </c>
       <c r="AL3" t="n">
-        <v>1729664</v>
+        <v>1608825</v>
       </c>
       <c r="AM3" t="n">
         <v>805900</v>
@@ -2885,79 +2883,77 @@
         <v>805900</v>
       </c>
       <c r="AO3" t="n">
-        <v>923764</v>
+        <v>802925</v>
       </c>
       <c r="AP3" t="n">
-        <v>236189</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>55082</v>
-      </c>
+        <v>11448</v>
+      </c>
+      <c r="AQ3" t="inlineStr"/>
       <c r="AR3" t="n">
-        <v>181107</v>
+        <v>12155</v>
       </c>
       <c r="AS3" t="n">
-        <v>-16336473</v>
+        <v>-39716689</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44773</v>
+        <v>45138</v>
       </c>
       <c r="B4" t="n">
-        <v>-9367198</v>
+        <v>-13567861</v>
       </c>
       <c r="C4" t="n">
-        <v>-367652</v>
+        <v>-362672</v>
       </c>
       <c r="D4" t="n">
-        <v>6359678</v>
+        <v>15583660</v>
       </c>
       <c r="E4" t="n">
-        <v>-95757</v>
+        <v>-32539</v>
       </c>
       <c r="F4" t="n">
+        <v>8327449</v>
+      </c>
+      <c r="G4" t="n">
         <v>6277321</v>
       </c>
-      <c r="G4" t="n">
-        <v>9652493</v>
-      </c>
       <c r="H4" t="n">
-        <v>-3375172</v>
+        <v>2050128</v>
       </c>
       <c r="I4" t="n">
-        <v>5992026</v>
+        <v>15220988</v>
       </c>
       <c r="J4" t="n">
-        <v>5992026</v>
+        <v>15220988</v>
       </c>
       <c r="K4" t="n">
-        <v>6359678</v>
+        <v>15583660</v>
       </c>
       <c r="L4" t="n">
-        <v>6359678</v>
+        <v>15583660</v>
       </c>
       <c r="M4" t="n">
-        <v>-367652</v>
+        <v>-362672</v>
       </c>
       <c r="N4" t="n">
-        <v>-367652</v>
+        <v>-362672</v>
       </c>
       <c r="O4" t="n">
-        <v>-367652</v>
+        <v>-362672</v>
       </c>
       <c r="P4" t="n">
-        <v>-95757</v>
+        <v>364462</v>
       </c>
       <c r="Q4" t="n">
-        <v>-95757</v>
+        <v>364462</v>
       </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>397001</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>397001</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -2966,52 +2962,52 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-95757</v>
+        <v>-32539</v>
       </c>
       <c r="X4" t="n">
-        <v>-95757</v>
+        <v>-32539</v>
       </c>
       <c r="Y4" t="n">
-        <v>-9271441</v>
+        <v>-13535322</v>
       </c>
       <c r="Z4" t="n">
-        <v>-9271441</v>
+        <v>-13535322</v>
       </c>
       <c r="AA4" t="n">
-        <v>1784673</v>
+        <v>-425516</v>
       </c>
       <c r="AB4" t="n">
-        <v>-111896</v>
+        <v>1183090</v>
       </c>
       <c r="AC4" t="n">
-        <v>1373471</v>
+        <v>-99732</v>
       </c>
       <c r="AD4" t="n">
-        <v>-313075</v>
+        <v>-358018</v>
       </c>
       <c r="AE4" t="n">
-        <v>-526082</v>
+        <v>-2198583</v>
       </c>
       <c r="AF4" t="n">
-        <v>1362255</v>
+        <v>1047727</v>
       </c>
       <c r="AG4" t="n">
-        <v>66632</v>
+        <v>22237</v>
       </c>
       <c r="AH4" t="n">
-        <v>1063840</v>
+        <v>950536</v>
       </c>
       <c r="AI4" t="n">
-        <v>-175000</v>
+        <v>-58333</v>
       </c>
       <c r="AJ4" t="n">
-        <v>26084830</v>
+        <v>346374</v>
       </c>
       <c r="AK4" t="n">
-        <v>1608825</v>
+        <v>1729664</v>
       </c>
       <c r="AL4" t="n">
-        <v>1608825</v>
+        <v>1729664</v>
       </c>
       <c r="AM4" t="n">
         <v>805900</v>
@@ -3020,148 +3016,152 @@
         <v>805900</v>
       </c>
       <c r="AO4" t="n">
-        <v>802925</v>
+        <v>923764</v>
       </c>
       <c r="AP4" t="n">
-        <v>11448</v>
-      </c>
-      <c r="AQ4" t="inlineStr"/>
+        <v>236189</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>55082</v>
+      </c>
       <c r="AR4" t="n">
-        <v>12155</v>
+        <v>181107</v>
       </c>
       <c r="AS4" t="n">
-        <v>-39716689</v>
+        <v>-16336473</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44408</v>
+        <v>45504</v>
       </c>
       <c r="B5" t="n">
-        <v>-12261429</v>
+        <v>-8573563</v>
       </c>
       <c r="C5" t="n">
-        <v>-514964</v>
+        <v>-381427</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>9256062</v>
       </c>
       <c r="E5" t="n">
-        <v>-566592</v>
+        <v>-429755</v>
       </c>
       <c r="F5" t="n">
-        <v>9652493</v>
+        <v>8628521</v>
       </c>
       <c r="G5" t="n">
-        <v>22407251</v>
+        <v>8327449</v>
       </c>
       <c r="H5" t="n">
-        <v>-12754758</v>
+        <v>301072</v>
       </c>
       <c r="I5" t="n">
-        <v>-514964</v>
+        <v>8874635</v>
       </c>
       <c r="J5" t="n">
-        <v>-514964</v>
+        <v>8874635</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>9256062</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>9256062</v>
       </c>
       <c r="M5" t="n">
-        <v>-514964</v>
+        <v>-381427</v>
       </c>
       <c r="N5" t="n">
-        <v>-514964</v>
+        <v>-381427</v>
       </c>
       <c r="O5" t="n">
-        <v>-514964</v>
+        <v>-381427</v>
       </c>
       <c r="P5" t="n">
-        <v>-544957</v>
+        <v>-429755</v>
       </c>
       <c r="Q5" t="n">
-        <v>-544957</v>
-      </c>
-      <c r="R5" t="n">
-        <v>21635</v>
-      </c>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
+        <v>-429755</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
       <c r="U5" t="n">
-        <v>-75000</v>
+        <v>-427955</v>
       </c>
       <c r="V5" t="n">
-        <v>-75000</v>
+        <v>-427955</v>
       </c>
       <c r="W5" t="n">
-        <v>-491592</v>
+        <v>-1800</v>
       </c>
       <c r="X5" t="n">
-        <v>-491592</v>
+        <v>-1800</v>
       </c>
       <c r="Y5" t="n">
-        <v>-11694837</v>
+        <v>-8143808</v>
       </c>
       <c r="Z5" t="n">
-        <v>-11694837</v>
+        <v>-8143808</v>
       </c>
       <c r="AA5" t="n">
-        <v>-2196307</v>
+        <v>-517696</v>
       </c>
       <c r="AB5" t="n">
-        <v>-119742</v>
+        <v>5470215</v>
       </c>
       <c r="AC5" t="n">
-        <v>-1083086</v>
+        <v>1471942</v>
       </c>
       <c r="AD5" t="n">
-        <v>601040</v>
+        <v>77656</v>
       </c>
       <c r="AE5" t="n">
-        <v>39744</v>
+        <v>-4522739</v>
       </c>
       <c r="AF5" t="n">
-        <v>-1634263</v>
+        <v>-3014770</v>
       </c>
       <c r="AG5" t="n">
-        <v>99065</v>
+        <v>22420</v>
       </c>
       <c r="AH5" t="n">
-        <v>1180231</v>
+        <v>1036744</v>
       </c>
       <c r="AI5" t="n">
-        <v>3977450</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>175042</v>
       </c>
       <c r="AK5" t="n">
-        <v>1812739</v>
+        <v>2109471</v>
       </c>
       <c r="AL5" t="n">
-        <v>1812739</v>
+        <v>2109471</v>
       </c>
       <c r="AM5" t="n">
-        <v>832817</v>
+        <v>805900</v>
       </c>
       <c r="AN5" t="n">
-        <v>832817</v>
+        <v>805900</v>
       </c>
       <c r="AO5" t="n">
-        <v>979922</v>
+        <v>1303571</v>
       </c>
       <c r="AP5" t="n">
-        <v>-5681</v>
+        <v>95066</v>
       </c>
       <c r="AQ5" t="inlineStr"/>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>95066</v>
       </c>
       <c r="AS5" t="n">
-        <v>-16562334</v>
+        <v>-11064855</v>
       </c>
     </row>
   </sheetData>
@@ -3676,212 +3676,212 @@
       </c>
       <c r="CV1" t="inlineStr">
         <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="CW1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="CX1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
           <t>regularMarketPrice</t>
         </is>
       </c>
-      <c r="CW1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
         <is>
           <t>shortName</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>longName</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="CZ1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DA1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DB1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>prevName</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>nameChangeDate</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>earningsTimestamp</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
         <is>
           <t>earningsCallTimestampStart</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>earningsCallTimestampEnd</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>isEarningsDateEstimate</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>prevName</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>nameChangeDate</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>earningsTimestamp</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
         </is>
       </c>
       <c r="EL1" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Peter  Evans', 'title': 'CEO &amp; Director', 'fiscalYear': 2025, 'totalPay': 465686, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Karen  Hersh', 'title': 'CFO &amp; Corporate Secretary', 'fiscalYear': 2025, 'totalPay': 252009, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Robert  Lex', 'title': 'Senior Vice President of Operations', 'fiscalYear': 2025, 'totalPay': 171318, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Louise  Johnson', 'title': 'Senior Vice President of Marketing', 'fiscalYear': 2025, 'totalPay': 152657, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Joshua  Douglas', 'title': 'Senior VP of Product &amp; Engineering', 'fiscalYear': 2025, 'totalPay': 283190, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Peter  Evans', 'title': 'CEO &amp; Director', 'fiscalYear': 2025, 'totalPay': 461495, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Karen  Hersh', 'title': 'CFO &amp; Corporate Secretary', 'fiscalYear': 2025, 'totalPay': 249741, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Robert  Lex', 'title': 'Senior Vice President of Operations', 'fiscalYear': 2025, 'totalPay': 169777, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Louise  Johnson', 'title': 'Senior Vice President of Marketing', 'fiscalYear': 2025, 'totalPay': 151283, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Joshua  Douglas', 'title': 'Senior VP of Product &amp; Engineering', 'fiscalYear': 2025, 'totalPay': 280642, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -3984,55 +3984,55 @@
         <v>4</v>
       </c>
       <c r="U2" t="n">
-        <v>0.287</v>
+        <v>0.38</v>
       </c>
       <c r="V2" t="n">
-        <v>0.28</v>
+        <v>0.372</v>
       </c>
       <c r="W2" t="n">
-        <v>0.28</v>
+        <v>0.372</v>
       </c>
       <c r="X2" t="n">
-        <v>0.28</v>
+        <v>0.372</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.287</v>
+        <v>0.38</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.28</v>
+        <v>0.372</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.28</v>
+        <v>0.372</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.28</v>
+        <v>0.372</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.378</v>
+        <v>1.404</v>
       </c>
       <c r="AE2" t="n">
-        <v>692</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>692</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.287</v>
+        <v>0.363</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.306</v>
+        <v>0.385</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -4041,10 +4041,10 @@
         <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>72772832</v>
+        <v>96693216</v>
       </c>
       <c r="AO2" t="n">
-        <v>76813144</v>
+        <v>101058290</v>
       </c>
       <c r="AP2" t="n">
         <v>0.186</v>
@@ -4059,13 +4059,13 @@
         <v>0.186</v>
       </c>
       <c r="AT2" t="n">
-        <v>4.2295594</v>
+        <v>4.0289664</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.27492</v>
+        <v>0.29582</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.35081</v>
+        <v>0.35143</v>
       </c>
       <c r="AW2" t="n">
         <v>0</v>
@@ -4082,31 +4082,31 @@
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>58030896</v>
+        <v>82011688</v>
       </c>
       <c r="BB2" t="n">
-        <v>-0.68888</v>
+        <v>-0.37573</v>
       </c>
       <c r="BC2" t="n">
-        <v>223578940</v>
+        <v>223564056</v>
       </c>
       <c r="BD2" t="n">
-        <v>259902980</v>
+        <v>259927980</v>
       </c>
       <c r="BE2" t="n">
         <v>0.1397</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.008240000000000001</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="BG2" t="n">
-        <v>259902980</v>
+        <v>259927980</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.046042893</v>
+        <v>0.045535773</v>
       </c>
       <c r="BI2" t="n">
-        <v>6.081286</v>
+        <v>8.169401000000001</v>
       </c>
       <c r="BJ2" t="n">
         <v>1753920000</v>
@@ -4115,25 +4115,25 @@
         <v>1785456000</v>
       </c>
       <c r="BL2" t="n">
-        <v>1769817600</v>
+        <v>1777507200</v>
       </c>
       <c r="BM2" t="n">
-        <v>-11852635</v>
+        <v>-9017447</v>
       </c>
       <c r="BN2" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.373</v>
+        <v>3.417</v>
       </c>
       <c r="BP2" t="n">
-        <v>-5.75</v>
+        <v>-11.184</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.010563374</v>
+        <v>1.0430107</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
@@ -4141,7 +4141,7 @@
         </is>
       </c>
       <c r="BT2" t="n">
-        <v>0.28</v>
+        <v>0.372</v>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
@@ -4149,58 +4149,58 @@
         </is>
       </c>
       <c r="BV2" t="n">
-        <v>15721093</v>
+        <v>15601050</v>
       </c>
       <c r="BW2" t="n">
         <v>0.06</v>
       </c>
       <c r="BX2" t="n">
-        <v>-10092588</v>
+        <v>-7332779</v>
       </c>
       <c r="BY2" t="n">
-        <v>979155</v>
+        <v>919529</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1.853</v>
+        <v>1.878</v>
       </c>
       <c r="CA2" t="n">
-        <v>2.547</v>
+        <v>2.543</v>
       </c>
       <c r="CB2" t="n">
-        <v>17205772</v>
+        <v>23999508</v>
       </c>
       <c r="CC2" t="n">
-        <v>5.112</v>
+        <v>4.802</v>
       </c>
       <c r="CD2" t="n">
-        <v>0.073</v>
+        <v>0.097</v>
       </c>
       <c r="CE2" t="n">
-        <v>-0.28114998</v>
+        <v>-0.22174999</v>
       </c>
       <c r="CF2" t="n">
-        <v>-0.8163</v>
+        <v>-0.69416</v>
       </c>
       <c r="CG2" t="n">
-        <v>10036707</v>
+        <v>14250699</v>
       </c>
       <c r="CH2" t="n">
-        <v>-3579549</v>
+        <v>-2616893</v>
       </c>
       <c r="CI2" t="n">
-        <v>-9721469</v>
+        <v>-6376499</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0.699</v>
+        <v>1.96</v>
       </c>
       <c r="CK2" t="n">
-        <v>0.58333</v>
+        <v>0.59379</v>
       </c>
       <c r="CL2" t="n">
-        <v>-0.58658004</v>
+        <v>-0.30554</v>
       </c>
       <c r="CM2" t="n">
-        <v>-0.39773998</v>
+        <v>-0.030739998</v>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
@@ -4240,159 +4240,159 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="CV2" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="CW2" t="inlineStr">
+      <c r="CV2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="CW2" t="n">
+        <v>1782108431</v>
+      </c>
+      <c r="CX2" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>finmb_379903309</t>
+        </is>
+      </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>Europe/Berlin</t>
+        </is>
+      </c>
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>CEST</t>
+        </is>
+      </c>
+      <c r="DB2" t="n">
+        <v>7200000</v>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>dr_market</t>
+        </is>
+      </c>
+      <c r="DD2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>-2.1052594</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="DG2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>1517468400000</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>-0.007999986000000001</v>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>0.372 - 0.372</t>
+        </is>
+      </c>
+      <c r="DK2" t="inlineStr">
         <is>
           <t>Xtract One Technologies Inc.  R</t>
         </is>
       </c>
-      <c r="CX2" t="inlineStr">
+      <c r="DL2" t="inlineStr">
         <is>
           <t>Xtract One Technologies Inc.</t>
         </is>
       </c>
-      <c r="CY2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="CZ2" t="n">
-        <v>1780380184</v>
-      </c>
-      <c r="DA2" t="inlineStr">
-        <is>
-          <t>FRA</t>
-        </is>
-      </c>
-      <c r="DB2" t="inlineStr">
-        <is>
-          <t>finmb_379903309</t>
-        </is>
-      </c>
-      <c r="DC2" t="inlineStr">
-        <is>
-          <t>Europe/Berlin</t>
-        </is>
-      </c>
-      <c r="DD2" t="inlineStr">
-        <is>
-          <t>CEST</t>
-        </is>
-      </c>
-      <c r="DE2" t="n">
-        <v>7200000</v>
-      </c>
-      <c r="DF2" t="inlineStr">
-        <is>
-          <t>dr_market</t>
-        </is>
-      </c>
-      <c r="DG2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DH2" t="n">
-        <v>1781186400</v>
-      </c>
-      <c r="DI2" t="n">
-        <v>1781186400</v>
-      </c>
-      <c r="DJ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DK2" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>0.0050800145</v>
-      </c>
-      <c r="DM2" t="n">
-        <v>0.018478157</v>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>PREPRE</t>
+        </is>
       </c>
       <c r="DN2" t="n">
-        <v>-0.07080999</v>
+        <v>0.07618001000000001</v>
       </c>
       <c r="DO2" t="n">
-        <v>-0.20184714</v>
+        <v>0.2575215</v>
       </c>
       <c r="DP2" t="n">
+        <v>0.02057001</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>0.058532313</v>
+      </c>
+      <c r="DR2" t="n">
         <v>15</v>
       </c>
-      <c r="DQ2" t="n">
+      <c r="DS2" t="n">
         <v>15</v>
       </c>
-      <c r="DR2" t="inlineStr">
+      <c r="DT2" t="inlineStr">
         <is>
           <t>Patriot One Technologies Inc.</t>
         </is>
       </c>
-      <c r="DS2" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="DT2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DU2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>1517468400000</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>-0.0069999993</v>
-      </c>
-      <c r="DX2" t="inlineStr">
-        <is>
-          <t>0.28 - 0.28</t>
-        </is>
-      </c>
-      <c r="DY2" t="inlineStr">
+      <c r="DU2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="DV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW2" t="inlineStr">
         <is>
           <t>Frankfurt</t>
         </is>
       </c>
+      <c r="DX2" t="n">
+        <v>45</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>0.186</v>
+      </c>
       <c r="DZ2" t="n">
-        <v>29</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>0.094</v>
+        <v>1</v>
+      </c>
+      <c r="EA2" t="inlineStr">
+        <is>
+          <t>0.186 - 0.585</t>
+        </is>
       </c>
       <c r="EB2" t="n">
-        <v>0.50537634</v>
-      </c>
-      <c r="EC2" t="inlineStr">
-        <is>
-          <t>0.186 - 0.585</t>
-        </is>
+        <v>-0.21299997</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>-0.3641025</v>
       </c>
       <c r="ED2" t="n">
-        <v>-0.30499998</v>
+        <v>104.30107</v>
       </c>
       <c r="EE2" t="n">
-        <v>-0.5213675</v>
+        <v>1781121600</v>
       </c>
       <c r="EF2" t="n">
-        <v>1.0563374</v>
+        <v>1781121600</v>
       </c>
       <c r="EG2" t="n">
         <v>1781121600</v>
       </c>
       <c r="EH2" t="n">
-        <v>1781121600</v>
+        <v>1781186400</v>
       </c>
       <c r="EI2" t="n">
-        <v>1781121600</v>
-      </c>
-      <c r="EJ2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
+        <v>1781186400</v>
+      </c>
+      <c r="EJ2" t="b">
+        <v>0</v>
       </c>
       <c r="EK2" t="n">
-        <v>-2.4390242</v>
+        <v>-0.02</v>
       </c>
       <c r="EL2" t="inlineStr"/>
     </row>
